--- a/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
+++ b/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/magangan/Latihan-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD300DA-66BD-E248-8CFD-3C05E8A2E4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342DFF8B-26AF-6548-AB7E-321FC97AEE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
     <sheet name="1_UNF" sheetId="2" r:id="rId2"/>
-    <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
-    <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
+    <sheet name="3_2NF" sheetId="4" r:id="rId3"/>
+    <sheet name="2_1NF" sheetId="3" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="148">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -462,6 +462,79 @@
 Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota
 Kode Produk -&gt; Nama Produk, Harga Satuan, Kode Kategori
 Kode Kategori, Nama Kategorri</t>
+  </si>
+  <si>
+    <t>tanggal</t>
+  </si>
+  <si>
+    <t>kode pelanggan</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>kota</t>
+  </si>
+  <si>
+    <t>nama produkk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kode kategori </t>
+  </si>
+  <si>
+    <t>nama kategori</t>
+  </si>
+  <si>
+    <t>harga satuan</t>
+  </si>
+  <si>
+    <t>No faktur</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>p003</t>
+  </si>
+  <si>
+    <t>p004</t>
+  </si>
+  <si>
+    <t>Buku Catatan A5</t>
+  </si>
+  <si>
+    <t>Pulpen Gel (isi 12)</t>
+  </si>
+  <si>
+    <t>k02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.000
+</t>
+  </si>
+  <si>
+    <t>alat tulis</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>tabel detail faktur</t>
+  </si>
+  <si>
+    <t>tabel produk</t>
+  </si>
+  <si>
+    <t>dijadikan 3 tabel karena sebelumnya ada 2 primery key (komposit)</t>
+  </si>
+  <si>
+    <t>nofaktur -&gt; tanggal, kode pelanggan email, kota ..dan Kode prodeuk --&gt; nama produk, kode kategori, nama katerri, harga satuan. ..dan No faktur,dan kode product -&gt; quantity</t>
+  </si>
+  <si>
+    <t>no faktur , kode produk</t>
   </si>
 </sst>
 </file>
@@ -469,7 +542,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -573,7 +646,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -624,11 +697,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -646,7 +730,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -666,7 +750,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -681,6 +765,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1457,6 +1544,419 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="23">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="23">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="26">
+        <v>150000</v>
+      </c>
+      <c r="L14" s="32"/>
+      <c r="M14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="23">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="26">
+        <v>750000</v>
+      </c>
+      <c r="L15" s="32"/>
+      <c r="M15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="23">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="26">
+        <v>150000</v>
+      </c>
+      <c r="L16" s="32"/>
+      <c r="M16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="23">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="O17" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="23">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" s="26">
+        <v>48000</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="O18" s="24"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M19" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N19" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="O19" s="24"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M20" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M21" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M23" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1464,7 +1964,8 @@
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17" x14ac:dyDescent="0.2">
@@ -1771,7 +2272,9 @@
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
+      <c r="C17" s="13">
+        <v>46280</v>
+      </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -1786,7 +2289,9 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
       <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
+      <c r="C18" s="13">
+        <v>46283</v>
+      </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
@@ -1801,7 +2306,9 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
+      <c r="C19" s="13">
+        <v>46285</v>
+      </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
@@ -1815,73 +2322,6 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C25" s="20"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
+++ b/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/magangan/Latihan-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342DFF8B-26AF-6548-AB7E-321FC97AEE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EA338B-5A16-B24A-BCE9-D6CB6238DBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
     <sheet name="1_UNF" sheetId="2" r:id="rId2"/>
-    <sheet name="3_2NF" sheetId="4" r:id="rId3"/>
-    <sheet name="2_1NF" sheetId="3" r:id="rId4"/>
+    <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
+    <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="160">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -535,6 +535,42 @@
   </si>
   <si>
     <t>no faktur , kode produk</t>
+  </si>
+  <si>
+    <t>tabel pelanggan</t>
+  </si>
+  <si>
+    <t>tabel kategori</t>
+  </si>
+  <si>
+    <t>tabel faktur</t>
+  </si>
+  <si>
+    <t>kode pelanggan (pk)</t>
+  </si>
+  <si>
+    <t>kode kategori (pk)</t>
+  </si>
+  <si>
+    <t>kode produk (pk)</t>
+  </si>
+  <si>
+    <t>No Faktur (pk)</t>
+  </si>
+  <si>
+    <t>No faktur (pk, fk)</t>
+  </si>
+  <si>
+    <t>kode produk (pk, fk)</t>
+  </si>
+  <si>
+    <t>kode pelanggan -&gt; email, kota .. No faktur -&gt; tanggal .. No faktur, kode produk --&gt; quantity .. Kode kategori --&gt; nama kategori .. Kode produk --&gt; nama produk</t>
+  </si>
+  <si>
+    <t>karena masih ada yang transitive dependency maka dipecah lagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kode pelanggan, kode katogri, no faktur, kode produk, </t>
   </si>
 </sst>
 </file>
@@ -613,7 +649,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -643,6 +679,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -712,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -765,9 +807,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1544,419 +1592,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="G11" t="s">
-        <v>144</v>
-      </c>
-      <c r="M11" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="M12" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="23">
-        <v>46266</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="O13" s="22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="23">
-        <v>46275</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="K14" s="26">
-        <v>150000</v>
-      </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="23">
-        <v>46277</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="K15" s="26">
-        <v>750000</v>
-      </c>
-      <c r="L15" s="32"/>
-      <c r="M15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N15" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="O15" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="23">
-        <v>46280</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="K16" s="26">
-        <v>150000</v>
-      </c>
-      <c r="L16" s="32"/>
-      <c r="M16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="O16" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="23">
-        <v>46283</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="M17" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="N17" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="O17" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="23">
-        <v>46285</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="K18" s="26">
-        <v>48000</v>
-      </c>
-      <c r="M18" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="N18" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="O18" s="24"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M19" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="N19" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="O19" s="24"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M20" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M21" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M22" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M23" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="M24" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2153,19 +1788,19 @@
       <c r="B14" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="23">
         <v>46275</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="22" t="s">
         <v>50</v>
       </c>
       <c r="H14" s="24" t="s">
@@ -2194,19 +1829,19 @@
       <c r="B15" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="23">
         <v>46275</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="22" t="s">
         <v>50</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -2235,44 +1870,44 @@
       <c r="B16" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="23">
         <v>46277</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="34">
         <v>1050000</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
-      <c r="C17" s="13">
+      <c r="C17" s="23">
         <v>46280</v>
       </c>
       <c r="D17" s="24"/>
@@ -2289,7 +1924,7 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
       <c r="B18" s="24"/>
-      <c r="C18" s="13">
+      <c r="C18" s="23">
         <v>46283</v>
       </c>
       <c r="D18" s="24"/>
@@ -2306,7 +1941,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="24"/>
       <c r="B19" s="24"/>
-      <c r="C19" s="13">
+      <c r="C19" s="23">
         <v>46285</v>
       </c>
       <c r="D19" s="24"/>
@@ -2328,9 +1963,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2338,57 +1973,818 @@
     <col min="3" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>144</v>
+      </c>
+      <c r="M11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="M12" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="N12" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="23">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="23">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="26">
+        <v>150000</v>
+      </c>
+      <c r="L14" s="33"/>
+      <c r="M14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="23">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="26">
+        <v>750000</v>
+      </c>
+      <c r="L15" s="33"/>
+      <c r="M15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="O15" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="23">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="26">
+        <v>150000</v>
+      </c>
+      <c r="L16" s="33"/>
+      <c r="M16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="23">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="M17" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="O17" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="23">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="K18" s="26">
+        <v>48000</v>
+      </c>
+      <c r="M18" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N18" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="O18" s="24"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M19" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N19" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="O19" s="24"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M20" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M21" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M23" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="M24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:L37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="16" t="s">
+        <v>159</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>157</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B8" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="K13" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="23">
+        <v>46266</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="23">
+        <v>46275</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="23">
+        <v>46277</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="L16" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="23">
+        <v>46280</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="L17" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="23">
+        <v>46283</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="L18" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="23">
+        <v>46285</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="L19" s="24"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J20" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="L20" s="24"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J21" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J22" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J23" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J25" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G31" s="35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
+++ b/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/magangan/Latihan-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EA338B-5A16-B24A-BCE9-D6CB6238DBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383D49F4-38CF-204E-A1D5-5C4E9AA5C47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,9 @@
     <sheet name="1_UNF" sheetId="2" r:id="rId2"/>
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
-    <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="query" sheetId="6" r:id="rId5"/>
+    <sheet name="DIagram" sheetId="7" r:id="rId6"/>
+    <sheet name="4_3NF" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="161">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -571,6 +573,111 @@
   </si>
   <si>
     <t xml:space="preserve">kode pelanggan, kode katogri, no faktur, kode produk, </t>
+  </si>
+  <si>
+    <t>IF DB_ID(N'SalesDB') IS NULL CREATE DATABASE SalesDB;
+USE SalesDB;
+-- hapus biar bisa dirun lg
+DROP TABLE IF EXISTS OrderDetail, [Order], Product, Category, Customer;
+GO
+-- tabel Customer,, customar dulu karena FKnya dipakai di tabel order
+CREATE TABLE Customer (
+CustomerID UNIQUEIDENTIFIER NOT NULL CONSTRAINT DF_Customer_CustomerID DEFAULT NEWSEQUENTIALID(), --biar berurutan,
+Name NVARCHAR(50) NOT NULL,
+Email VARCHAR(100) NULL,
+City VARCHAR(50) NOT NULL,
+CONSTRAINT PK_Customer PRIMARY KEY (CustomerID)
+);
+GO
+-- INSERT DATA CUSTOMER
+INSERT INTO Customer (Name, Email, City) VALUES
+('Budi', 'budi@mail.com', 'Jakarta'),
+('Siti', 'siti@mail.com', 'Bandung'),
+('Andi', 'andi@mail.com', 'Surabaya');
+GO
+SELECT * from Customer;
+-- filtered unique index untuk Customer.Email (biar email unik)
+CREATE UNIQUE NONCLUSTERED INDEX UX_Customer_Email
+ON Customer (Email)
+WHERE Email IS NOT NULL;
+GO
+-- tabel Category
+CREATE TABLE Category (
+CategoryID  NVARCHAR(10) NOT NULL CONSTRAINT PK_Category PRIMARY KEY ,
+CategoryName  NVARCHAR(50) NOT NULL,
+SubCategoryID NVARCHAR(10) NULL,
+CONSTRAINT FK_Category_SubCategory FOREIGN KEY (SubCategoryID) REFERENCES Category (CategoryID)
+    -- yang FK ADA referencenya
+);
+GO
+-- INSERT DATA Category
+INSERT INTO Category (CategoryID, CategoryName) VALUES
+('K01', 'Elektronik'),
+('K03', 'Aksesoris Komputer'),
+('K02', 'alat Tulis');
+GO
+-- tabel Product
+CREATE TABLE Product (
+ProductID INT IDENTITY(1,1) NOT NULL CONSTRAINT PK_Product PRIMARY KEY,
+CategoryID  NVARCHAR(10) NOT NULL,
+ProductName NVARCHAR(100) NOT NULL,
+UnitPrice  DECIMAL(12,2) NOT NULL CONSTRAINT CK_Product_UnitPrice CHECK (UnitPrice &gt;= 0),
+Stock INT NOT NULL CONSTRAINT DF_Product_Stock DEFAULT 0,
+CONSTRAINT FK_Product_Category FOREIGN KEY (CategoryID) REFERENCES Category (CategoryID),
+CONSTRAINT CK_Product_Stock CHECK (Stock &gt;= 0)
+);
+GO
+-- INSERT DATA pRODUCT
+INSERT INTO Product  (CategoryID, ProductName, UnitPrice, Stock) VALUES
+('K01','Monitor 24 inchi', '1850000', '5'),
+('K03','Mouse wireless', '150000', '4'),
+('K03','Keyboard Mechanich', '750000', '6'),
+('K02','Buku Catatan', '48000', '4'),
+('K02','Pulpen', '25000','4');
+GO
+SELECT * FROM  Product;
+-- tabel Order
+CREATE TABLE [Order] ( --harus dikasih kurung agar tidak tertukar dengan sytax order
+OrderID    UNIQUEIDENTIFIER NOT NULL CONSTRAINT DF_Order_OrderID DEFAULT NEWSEQUENTIALID(),
+CustomerID UNIQUEIDENTIFIER NOT NULL,
+OrderDate  DATETIME2(0) NOT NULL CONSTRAINT DF_Order_OrderDate DEFAULT SYSDATETIME(),
+CONSTRAINT PK_Order PRIMARY KEY (OrderID),
+CONSTRAINT FK_Order_Customer FOREIGN KEY (CustomerID) REFERENCES Customer (CustomerID)
+);
+GO
+-- INSERT Order (CustomerID Budi diambil otomatis)
+-- INSERT Order (CustomerID diambil otomatis dari email)
+INSERT INTO [Order] (CustomerID, OrderDate)
+SELECT CustomerID, '2022-02-03' FROM Customer WHERE Email = 'budi@mail.com';
+INSERT INTO [Order] (CustomerID, OrderDate)
+SELECT CustomerID, '2022-02-05' FROM Customer WHERE Email = 'siti@mail.com';
+INSERT INTO [Order] (CustomerID, OrderDate)
+SELECT CustomerID, '2022-02-07' FROM Customer WHERE Email = 'andi@mail.com';
+SELECT  * from [Order];
+-- tabel OrderDetail
+CREATE TABLE OrderDetail (
+OrderID UNIQUEIDENTIFIER NOT NULL CONSTRAINT FK_OrderDetail_Order FOREIGN KEY REFERENCES [Order](OrderID),
+ProductID INT NOT NULL,
+Quantity INT NOT NULL CONSTRAINT CK_OrderDetail_Quantity CHECK (Quantity &gt; 0),
+UnitPrice DECIMAL(12,2) NOT NULL,
+CONSTRAINT PK_OrderDetail PRIMARY KEY (OrderID, ProductID),
+CONSTRAINT FK_OrderDetail_Product FOREIGN KEY (ProductID) REFERENCES Product(ProductID),
+);
+GO
+-- INSERT OrderDetail (OrderID diambil otomatis dari tabel Order)
+INSERT INTO OrderDetail(OrderID, ProductID, Quantity, UnitPrice) VALUES
+('D20D433E-F36B-1410-8551-00AAD0A8C3EB', 1, 3, 1850000),
+('D20D433E-F36B-1410-8551-00AAD0A8C3EB', 2, 4, 150000),
+('D50D433E-F36B-1410-8551-00AAD0A8C3EB', 3, 6, 750000),
+('D80D433E-F36B-1410-8551-00AAD0A8C3EB', 4, 4, 48000);
+GO
+SELECT * from OrderDetail;
+-- cekk
+SELECT * FROM Customer;
+SELECT * FROM Category;
+SELECT * FROM Product;
+SELECT * FROM [Order];
+SELECT * FROM OrderDetail;</t>
   </si>
 </sst>
 </file>
@@ -754,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -807,9 +914,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -831,6 +936,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>10590</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Gambar 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BE1F51C-4B2A-BAE3-F5B4-ACCBDD625C9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14044090" cy="7886700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1900,7 +2060,7 @@
       <c r="L16" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="32">
         <v>1050000</v>
       </c>
     </row>
@@ -2040,7 +2200,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="24" t="s">
@@ -2152,7 +2312,7 @@
       <c r="K14" s="26">
         <v>150000</v>
       </c>
-      <c r="L14" s="33"/>
+      <c r="L14" s="31"/>
       <c r="M14" s="22" t="s">
         <v>35</v>
       </c>
@@ -2194,7 +2354,7 @@
       <c r="K15" s="26">
         <v>750000</v>
       </c>
-      <c r="L15" s="33"/>
+      <c r="L15" s="31"/>
       <c r="M15" s="24" t="s">
         <v>46</v>
       </c>
@@ -2221,7 +2381,7 @@
       <c r="E16" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="24" t="s">
         <v>120</v>
       </c>
       <c r="H16" s="24" t="s">
@@ -2236,7 +2396,7 @@
       <c r="K16" s="26">
         <v>150000</v>
       </c>
-      <c r="L16" s="33"/>
+      <c r="L16" s="31"/>
       <c r="M16" s="24" t="s">
         <v>46</v>
       </c>
@@ -2263,7 +2423,7 @@
       <c r="E17" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="24" t="s">
         <v>134</v>
       </c>
       <c r="H17" s="24" t="s">
@@ -2304,7 +2464,7 @@
       <c r="E18" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="24" t="s">
         <v>135</v>
       </c>
       <c r="H18" s="24" t="s">
@@ -2377,6 +2537,34 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D22CDAA-5CA1-CB40-88AF-2697A828ADCE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="69.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D2A5B6B-2989-B343-A7CC-C771880881C0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2446,7 +2634,7 @@
       <c r="A11" s="18"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="3" t="s">
         <v>148</v>
       </c>
       <c r="F12" t="s">
@@ -2457,28 +2645,28 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="K13" s="35" t="s">
+      <c r="K13" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="L13" s="35" t="s">
+      <c r="L13" s="33" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2689,16 +2877,16 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="G31" s="35" t="s">
+      <c r="G31" s="33" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2751,7 +2939,7 @@
       <c r="B35" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="32" t="s">
+      <c r="F35" s="24" t="s">
         <v>120</v>
       </c>
       <c r="G35" s="24" t="s">
@@ -2765,7 +2953,7 @@
       <c r="B36" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F36" s="32" t="s">
+      <c r="F36" s="24" t="s">
         <v>134</v>
       </c>
       <c r="G36" s="24" t="s">
@@ -2779,7 +2967,7 @@
       <c r="B37" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F37" s="32" t="s">
+      <c r="F37" s="24" t="s">
         <v>135</v>
       </c>
       <c r="G37" s="24" t="s">

--- a/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
+++ b/Normalisasi_SalesDB_Muh. Fatkhi A.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Documents/magangan/Latihan-database/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alex/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383D49F4-38CF-204E-A1D5-5C4E9AA5C47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06331DCF-2068-0848-BCD7-0696F79B199A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,8 @@
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="query" sheetId="6" r:id="rId5"/>
     <sheet name="DIagram" sheetId="7" r:id="rId6"/>
-    <sheet name="4_3NF" sheetId="5" r:id="rId7"/>
+    <sheet name="jawaban latihan query" sheetId="9" r:id="rId7"/>
+    <sheet name="4_3NF" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="162">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -596,7 +597,7 @@
 ('Andi', 'andi@mail.com', 'Surabaya');
 GO
 SELECT * from Customer;
--- filtered unique index untuk Customer.Email (biar email unik)
+-- filtered unique index 
 CREATE UNIQUE NONCLUSTERED INDEX UX_Customer_Email
 ON Customer (Email)
 WHERE Email IS NOT NULL;
@@ -637,7 +638,7 @@
 GO
 SELECT * FROM  Product;
 -- tabel Order
-CREATE TABLE [Order] ( --harus dikasih kurung agar tidak tertukar dengan sytax order
+CREATE TABLE [Order] (
 OrderID    UNIQUEIDENTIFIER NOT NULL CONSTRAINT DF_Order_OrderID DEFAULT NEWSEQUENTIALID(),
 CustomerID UNIQUEIDENTIFIER NOT NULL,
 OrderDate  DATETIME2(0) NOT NULL CONSTRAINT DF_Order_OrderDate DEFAULT SYSDATETIME(),
@@ -645,14 +646,14 @@
 CONSTRAINT FK_Order_Customer FOREIGN KEY (CustomerID) REFERENCES Customer (CustomerID)
 );
 GO
--- INSERT Order (CustomerID Budi diambil otomatis)
--- INSERT Order (CustomerID diambil otomatis dari email)
+-- INSERT Order 
 INSERT INTO [Order] (CustomerID, OrderDate)
 SELECT CustomerID, '2022-02-03' FROM Customer WHERE Email = 'budi@mail.com';
 INSERT INTO [Order] (CustomerID, OrderDate)
 SELECT CustomerID, '2022-02-05' FROM Customer WHERE Email = 'siti@mail.com';
 INSERT INTO [Order] (CustomerID, OrderDate)
 SELECT CustomerID, '2022-02-07' FROM Customer WHERE Email = 'andi@mail.com';
+GO
 SELECT  * from [Order];
 -- tabel OrderDetail
 CREATE TABLE OrderDetail (
@@ -661,23 +662,83 @@
 Quantity INT NOT NULL CONSTRAINT CK_OrderDetail_Quantity CHECK (Quantity &gt; 0),
 UnitPrice DECIMAL(12,2) NOT NULL,
 CONSTRAINT PK_OrderDetail PRIMARY KEY (OrderID, ProductID),
-CONSTRAINT FK_OrderDetail_Product FOREIGN KEY (ProductID) REFERENCES Product(ProductID),
+CONSTRAINT FK_OrderDetail_Product FOREIGN KEY (ProductID) REFERENCES Product(ProductID)
 );
 GO
--- INSERT OrderDetail (OrderID diambil otomatis dari tabel Order)
+-- INSERT OrderDetail 
 INSERT INTO OrderDetail(OrderID, ProductID, Quantity, UnitPrice) VALUES
-('D20D433E-F36B-1410-8551-00AAD0A8C3EB', 1, 3, 1850000),
-('D20D433E-F36B-1410-8551-00AAD0A8C3EB', 2, 4, 150000),
-('D50D433E-F36B-1410-8551-00AAD0A8C3EB', 3, 6, 750000),
-('D80D433E-F36B-1410-8551-00AAD0A8C3EB', 4, 4, 48000);
+('700e433e-f36b-1410-8551-00aad0a8c3eb', 1, 3, 1850000), 
+('700e433e-f36b-1410-8551-00aad0a8c3eb', 2, 4, 150000),  
+('730e433e-f36b-1410-8551-00aad0a8c3eb', 3, 6, 750000),  
 GO
-SELECT * from OrderDetail;
+SELECT * from OrderDetail;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+INSERT INTO Category (CategoryID, CategoryName)
+OUTPUT inserted.CategoryID, inserted.CategoryName
+VALUES ('K04', N'ok'), ('K05', N'cek');
+DELETE FROM Category
+OUTPUT deleted.CategoryID, deleted.CategoryName
+WHERE CategoryID IN ('K04', 'K05');
+GO
+-- harga produk pertama jadi 2 kali liapt
+UPDATE Product
+SET UnitPrice = UnitPrice * 2
+OUTPUT deleted.UnitPrice AS HargaLama,
+       inserted.UnitPrice AS HargaBaru
+WHERE ProductID = 1;
+GO
+-- =============================================
+-- customer baru
+INSERT INTO Customer (Name, Email, City)
+OUTPUT inserted.CustomerID, inserted.Name, inserted.Email, inserted.City
+VALUES ('Dewi Lestari', NULL, 'Jakarta');
+GO
+SELECT * FROM Customer 
+-- produk baruu
+INSERT INTO Product (CategoryID, ProductName, UnitPrice, Stock)
+OUTPUT inserted.ProductID, inserted.ProductName, inserted.UnitPrice, inserted.Stock
+VALUES ('K03', 'Headset', 375000, 40);
+GO
+SELECT * FROM Product  
+-- update stoknya
+UPDATE Product SET Stock = 15 WHERE ProductName = 'Monitor 24 inchi';
+UPDATE Product SET Stock = 40 WHERE ProductName = 'Headset';
+UPDATE Product SET Stock = 200 WHERE ProductName = 'Buku Catatan';
+UPDATE Product SET Stock = 150 WHERE ProductName = 'Pulpen';
+UPDATE Product SET Stock = 60 WHERE ProductName = 'Mouse wireless';
+UPDATE Product SET Stock = 25 WHERE ProductName = 'Keyboard Mechanich';
+GO
 -- cekk
 SELECT * FROM Customer;
 SELECT * FROM Category;
 SELECT * FROM Product;
 SELECT * FROM [Order];
-SELECT * FROM OrderDetail;</t>
+SELECT * FROM OrderDetail;
+-- 1
+INSERT INTO OrderDetail (OrderID, ProductID, Quantity, UnitPrice) VALUES
+('280E433E-F36B-1410-8551-00AAD0A8C3EB', 5, 0, 25000);
+-- 2
+INSERT INTO [Order] (CustomerID, OrderDate) VALUES (99, '2022-02-10');
+--3
+INSERT INTO Product (CategoryID, ProductName, UnitPrice, Stock)
+VALUES ('K03', 'Webcam', 300000, -5);
+-- 4
+BEGIN TRAN;
+INSERT INTO Customer (Name, Email, City)
+OUTPUT inserted.CustomerID, inserted.Name, inserted.Email
+VALUES ('Rina Uji', NULL, 'Bogor');
+SELECT * FROM Customer WHERE Email IS NULL;  
+ROLLBACK;
+-- 5
+BEGIN TRAN;
+INSERT INTO Customer (Name, Email, City)
+VALUES ('Budi Palsu', 'budi@mail.com', 'Depok');
+ROLLBACK;
+-- cek: 
+SELECT * FROM Customer;
+SELECT @@TRANCOUNT AS TransaksiTerbuka;  -</t>
   </si>
 </sst>
 </file>
@@ -861,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -921,6 +982,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2538,18 +2602,246 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D22CDAA-5CA1-CB40-88AF-2697A828ADCE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="69.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
         <v>160</v>
       </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="35"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2565,6 +2857,294 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5F8F9C-A598-3C48-A4F2-3D10CECF3220}">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="35"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="35"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
